--- a/infra/mock-data/school-connect-mock-import.xlsx
+++ b/infra/mock-data/school-connect-mock-import.xlsx
@@ -9,13 +9,14 @@
     <sheet sheetId="3" name="Users" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Students" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Fee Structures" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Teachers" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="747">
   <si>
     <t>School Connect — Bulk Onboarding Template</t>
   </si>
@@ -2226,6 +2227,36 @@
   </si>
   <si>
     <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>Teacher Name*</t>
+  </si>
+  <si>
+    <t>Phone Number*</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Subject Name*</t>
+  </si>
+  <si>
+    <t>Is Class Teacher</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Social Studies</t>
   </si>
 </sst>
 </file>
@@ -7124,4 +7155,230 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B1" t="s">
+        <v>738</v>
+      </c>
+      <c r="C1" t="s">
+        <v>739</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>724</v>
+      </c>
+      <c r="F1" t="s">
+        <v>740</v>
+      </c>
+      <c r="G1" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>742</v>
+      </c>
+      <c r="G2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>744</v>
+      </c>
+      <c r="G3" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>745</v>
+      </c>
+      <c r="G4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>746</v>
+      </c>
+      <c r="G5" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>742</v>
+      </c>
+      <c r="G6" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>744</v>
+      </c>
+      <c r="G7" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>745</v>
+      </c>
+      <c r="G8" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>746</v>
+      </c>
+      <c r="G9" t="s">
+        <v>743</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/infra/mock-data/school-connect-mock-import.xlsx
+++ b/infra/mock-data/school-connect-mock-import.xlsx
@@ -7,8 +7,8 @@
     <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Classes" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Users" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Students" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Fee Structures" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="Fee Structures" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="Students" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Teachers" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="771">
   <si>
     <t>School Connect — Bulk Onboarding Template</t>
   </si>
@@ -300,6 +300,45 @@
     <t>+919800001020</t>
   </si>
   <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Term*</t>
+  </si>
+  <si>
+    <t>Fee Component*</t>
+  </si>
+  <si>
+    <t>Amount*</t>
+  </si>
+  <si>
+    <t>Due Date*</t>
+  </si>
+  <si>
+    <t>Late Fee</t>
+  </si>
+  <si>
+    <t>Term 1</t>
+  </si>
+  <si>
+    <t>Tuition</t>
+  </si>
+  <si>
+    <t>2025-06-15</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Activities</t>
+  </si>
+  <si>
+    <t>Term 2</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
     <t>Student Name*</t>
   </si>
   <si>
@@ -312,12 +351,39 @@
     <t>Parent Name*</t>
   </si>
   <si>
+    <t>Guardian 1 Relation</t>
+  </si>
+  <si>
     <t>Parent Mobile Number*</t>
   </si>
   <si>
     <t>Parent Email</t>
   </si>
   <si>
+    <t>Parent Profession</t>
+  </si>
+  <si>
+    <t>Guardian 2 Name</t>
+  </si>
+  <si>
+    <t>Guardian 2 Relation</t>
+  </si>
+  <si>
+    <t>Guardian 2 Mobile Number</t>
+  </si>
+  <si>
+    <t>Guardian 2 Email</t>
+  </si>
+  <si>
+    <t>Guardian 2 Profession</t>
+  </si>
+  <si>
+    <t>Blood Group</t>
+  </si>
+  <si>
+    <t>Caste</t>
+  </si>
+  <si>
     <t>Vivaan Singh</t>
   </si>
   <si>
@@ -330,12 +396,21 @@
     <t>Aryan Singh</t>
   </si>
   <si>
+    <t>Father</t>
+  </si>
+  <si>
     <t>+919800002001</t>
   </si>
   <si>
     <t>aryan.singh1@example.com</t>
   </si>
   <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
     <t>Aditya Patel</t>
   </si>
   <si>
@@ -354,6 +429,12 @@
     <t>dhruv.patel2@example.com</t>
   </si>
   <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>OBC</t>
+  </si>
+  <si>
     <t>Vihaan Reddy</t>
   </si>
   <si>
@@ -372,6 +453,12 @@
     <t>karthik.reddy3@example.com</t>
   </si>
   <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
     <t>Arjun Iyer</t>
   </si>
   <si>
@@ -390,6 +477,12 @@
     <t>manav.iyer4@example.com</t>
   </si>
   <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
     <t>Reyansh Nair</t>
   </si>
   <si>
@@ -408,6 +501,12 @@
     <t>nikhil.nair5@example.com</t>
   </si>
   <si>
+    <t>AB+</t>
+  </si>
+  <si>
+    <t>EWS</t>
+  </si>
+  <si>
     <t>Krishna Rao</t>
   </si>
   <si>
@@ -426,6 +525,12 @@
     <t>om.rao6@example.com</t>
   </si>
   <si>
+    <t>AB-</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
     <t>Ishaan Mehta</t>
   </si>
   <si>
@@ -444,6 +549,9 @@
     <t>pranav.mehta7@example.com</t>
   </si>
   <si>
+    <t>O+</t>
+  </si>
+  <si>
     <t>Rohan Joshi</t>
   </si>
   <si>
@@ -462,6 +570,9 @@
     <t>rudra.joshi8@example.com</t>
   </si>
   <si>
+    <t>O-</t>
+  </si>
+  <si>
     <t>Kabir Desai</t>
   </si>
   <si>
@@ -2188,45 +2299,6 @@
   </si>
   <si>
     <t>manav.joshi104@example.com</t>
-  </si>
-  <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>Term*</t>
-  </si>
-  <si>
-    <t>Fee Component*</t>
-  </si>
-  <si>
-    <t>Amount*</t>
-  </si>
-  <si>
-    <t>Due Date*</t>
-  </si>
-  <si>
-    <t>Late Fee</t>
-  </si>
-  <si>
-    <t>Term 1</t>
-  </si>
-  <si>
-    <t>Tuition</t>
-  </si>
-  <si>
-    <t>2025-06-15</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
-    <t>Activities</t>
-  </si>
-  <si>
-    <t>Term 2</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
   </si>
   <si>
     <t>Teacher Name*</t>
@@ -3262,48 +3334,87 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:Q105"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K1" t="s">
+        <v>115</v>
+      </c>
+      <c r="L1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M1" t="s">
+        <v>117</v>
+      </c>
+      <c r="N1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O1" t="s">
+        <v>119</v>
+      </c>
+      <c r="P1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -3312,24 +3423,51 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="H2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="I2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -3338,24 +3476,51 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F3" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="G3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="I3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -3364,24 +3529,51 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="F4" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="G4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="H4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="I4" t="s">
+        <v>144</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -3390,24 +3582,51 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="F5" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="G5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="I5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -3416,24 +3635,51 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" t="s">
         <v>126</v>
       </c>
-      <c r="F6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G6" t="s">
-        <v>128</v>
-      </c>
       <c r="H6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+      <c r="I6" t="s">
+        <v>160</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -3442,24 +3688,51 @@
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="F7" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="G7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="I7" t="s">
+        <v>168</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -3468,24 +3741,51 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="F8" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="G8" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="I8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -3494,24 +3794,51 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="F9" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="G9" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="I9" t="s">
+        <v>183</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -3520,24 +3847,51 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="F10" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="G10" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="H10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="I10" t="s">
+        <v>190</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -3546,24 +3900,51 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="F11" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="G11" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="H11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="I11" t="s">
+        <v>196</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -3572,24 +3953,51 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
+        <v>199</v>
+      </c>
+      <c r="F12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G12" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" t="s">
+        <v>201</v>
+      </c>
+      <c r="I12" t="s">
+        <v>202</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q12" t="s">
         <v>162</v>
       </c>
-      <c r="F12" t="s">
-        <v>163</v>
-      </c>
-      <c r="G12" t="s">
-        <v>164</v>
-      </c>
-      <c r="H12" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="B13" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -3598,24 +4006,51 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="F13" t="s">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="G13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" t="s">
+        <v>207</v>
+      </c>
+      <c r="I13" t="s">
+        <v>208</v>
+      </c>
+      <c r="J13" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13" t="s">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q13" t="s">
         <v>170</v>
       </c>
-      <c r="H13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="B14" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
@@ -3624,24 +4059,51 @@
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="F14" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="G14" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="H14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="I14" t="s">
+        <v>214</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
@@ -3650,24 +4112,51 @@
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="F15" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="G15" t="s">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="H15" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+      <c r="I15" t="s">
+        <v>220</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" t="s">
+        <v>1</v>
+      </c>
+      <c r="O15" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="B16" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
@@ -3676,24 +4165,51 @@
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="F16" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="G16" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="H16" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+      <c r="I16" t="s">
+        <v>226</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" t="s">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="B17" t="s">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -3702,24 +4218,51 @@
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="F17" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="G17" t="s">
-        <v>194</v>
+        <v>126</v>
       </c>
       <c r="H17" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+      <c r="I17" t="s">
+        <v>232</v>
+      </c>
+      <c r="J17" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
+        <v>1</v>
+      </c>
+      <c r="M17" t="s">
+        <v>1</v>
+      </c>
+      <c r="N17" t="s">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
+        <v>1</v>
+      </c>
+      <c r="P17" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="B18" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
@@ -3728,24 +4271,51 @@
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="F18" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="G18" t="s">
-        <v>200</v>
+        <v>126</v>
       </c>
       <c r="H18" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I18" t="s">
+        <v>238</v>
+      </c>
+      <c r="J18" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="B19" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
@@ -3754,24 +4324,51 @@
         <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="F19" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="G19" t="s">
-        <v>206</v>
+        <v>126</v>
       </c>
       <c r="H19" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+      <c r="I19" t="s">
+        <v>244</v>
+      </c>
+      <c r="J19" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19" t="s">
+        <v>1</v>
+      </c>
+      <c r="O19" t="s">
+        <v>1</v>
+      </c>
+      <c r="P19" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -3780,24 +4377,51 @@
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="F20" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="G20" t="s">
-        <v>212</v>
+        <v>126</v>
       </c>
       <c r="H20" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+      <c r="I20" t="s">
+        <v>250</v>
+      </c>
+      <c r="J20" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
+        <v>1</v>
+      </c>
+      <c r="M20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P20" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
@@ -3806,24 +4430,51 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="F21" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="G21" t="s">
-        <v>218</v>
+        <v>126</v>
       </c>
       <c r="H21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="I21" t="s">
+        <v>256</v>
+      </c>
+      <c r="J21" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" t="s">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
+        <v>1</v>
+      </c>
+      <c r="P21" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -3832,24 +4483,51 @@
         <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="F22" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="G22" t="s">
-        <v>224</v>
+        <v>126</v>
       </c>
       <c r="H22" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="I22" t="s">
+        <v>262</v>
+      </c>
+      <c r="J22" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" t="s">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N22" t="s">
+        <v>1</v>
+      </c>
+      <c r="O22" t="s">
+        <v>1</v>
+      </c>
+      <c r="P22" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -3858,24 +4536,51 @@
         <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="F23" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="G23" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
       <c r="H23" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="I23" t="s">
+        <v>268</v>
+      </c>
+      <c r="J23" t="s">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" t="s">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
+        <v>1</v>
+      </c>
+      <c r="N23" t="s">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>1</v>
+      </c>
+      <c r="P23" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="C24" t="s">
         <v>22</v>
@@ -3884,24 +4589,51 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="F24" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="G24" t="s">
-        <v>236</v>
+        <v>126</v>
       </c>
       <c r="H24" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="I24" t="s">
+        <v>274</v>
+      </c>
+      <c r="J24" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" t="s">
+        <v>1</v>
+      </c>
+      <c r="M24" t="s">
+        <v>1</v>
+      </c>
+      <c r="N24" t="s">
+        <v>1</v>
+      </c>
+      <c r="O24" t="s">
+        <v>1</v>
+      </c>
+      <c r="P24" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s">
-        <v>239</v>
+        <v>276</v>
       </c>
       <c r="C25" t="s">
         <v>22</v>
@@ -3910,24 +4642,51 @@
         <v>19</v>
       </c>
       <c r="E25" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="F25" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="G25" t="s">
-        <v>242</v>
+        <v>126</v>
       </c>
       <c r="H25" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="I25" t="s">
+        <v>280</v>
+      </c>
+      <c r="J25" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" t="s">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>1</v>
+      </c>
+      <c r="N25" t="s">
+        <v>1</v>
+      </c>
+      <c r="O25" t="s">
+        <v>1</v>
+      </c>
+      <c r="P25" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>244</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s">
-        <v>245</v>
+        <v>282</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
@@ -3936,24 +4695,51 @@
         <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="F26" t="s">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="G26" t="s">
-        <v>248</v>
+        <v>126</v>
       </c>
       <c r="H26" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="I26" t="s">
+        <v>286</v>
+      </c>
+      <c r="J26" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" t="s">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>1</v>
+      </c>
+      <c r="N26" t="s">
+        <v>1</v>
+      </c>
+      <c r="O26" t="s">
+        <v>1</v>
+      </c>
+      <c r="P26" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="C27" t="s">
         <v>22</v>
@@ -3962,24 +4748,51 @@
         <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="F27" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="G27" t="s">
-        <v>254</v>
+        <v>126</v>
       </c>
       <c r="H27" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+      <c r="I27" t="s">
+        <v>292</v>
+      </c>
+      <c r="J27" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" t="s">
+        <v>1</v>
+      </c>
+      <c r="M27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N27" t="s">
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
+        <v>1</v>
+      </c>
+      <c r="P27" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="B28" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="C28" t="s">
         <v>24</v>
@@ -3988,24 +4801,51 @@
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="F28" t="s">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="G28" t="s">
-        <v>260</v>
+        <v>126</v>
       </c>
       <c r="H28" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+      <c r="I28" t="s">
+        <v>298</v>
+      </c>
+      <c r="J28" t="s">
+        <v>1</v>
+      </c>
+      <c r="K28" t="s">
+        <v>1</v>
+      </c>
+      <c r="L28" t="s">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>1</v>
+      </c>
+      <c r="N28" t="s">
+        <v>1</v>
+      </c>
+      <c r="O28" t="s">
+        <v>1</v>
+      </c>
+      <c r="P28" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>262</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="C29" t="s">
         <v>24</v>
@@ -4014,24 +4854,51 @@
         <v>19</v>
       </c>
       <c r="E29" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="F29" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="G29" t="s">
-        <v>266</v>
+        <v>126</v>
       </c>
       <c r="H29" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+      <c r="I29" t="s">
+        <v>304</v>
+      </c>
+      <c r="J29" t="s">
+        <v>1</v>
+      </c>
+      <c r="K29" t="s">
+        <v>1</v>
+      </c>
+      <c r="L29" t="s">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>1</v>
+      </c>
+      <c r="N29" t="s">
+        <v>1</v>
+      </c>
+      <c r="O29" t="s">
+        <v>1</v>
+      </c>
+      <c r="P29" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="C30" t="s">
         <v>24</v>
@@ -4040,24 +4907,51 @@
         <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="F30" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="G30" t="s">
-        <v>272</v>
+        <v>126</v>
       </c>
       <c r="H30" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="I30" t="s">
+        <v>310</v>
+      </c>
+      <c r="J30" t="s">
+        <v>1</v>
+      </c>
+      <c r="K30" t="s">
+        <v>1</v>
+      </c>
+      <c r="L30" t="s">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>1</v>
+      </c>
+      <c r="N30" t="s">
+        <v>1</v>
+      </c>
+      <c r="O30" t="s">
+        <v>1</v>
+      </c>
+      <c r="P30" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="C31" t="s">
         <v>24</v>
@@ -4066,24 +4960,51 @@
         <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
       <c r="F31" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="G31" t="s">
-        <v>278</v>
+        <v>126</v>
       </c>
       <c r="H31" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+      <c r="I31" t="s">
+        <v>316</v>
+      </c>
+      <c r="J31" t="s">
+        <v>1</v>
+      </c>
+      <c r="K31" t="s">
+        <v>1</v>
+      </c>
+      <c r="L31" t="s">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>1</v>
+      </c>
+      <c r="N31" t="s">
+        <v>1</v>
+      </c>
+      <c r="O31" t="s">
+        <v>1</v>
+      </c>
+      <c r="P31" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s">
-        <v>281</v>
+        <v>318</v>
       </c>
       <c r="C32" t="s">
         <v>24</v>
@@ -4092,24 +5013,51 @@
         <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>282</v>
+        <v>319</v>
       </c>
       <c r="F32" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="G32" t="s">
-        <v>284</v>
+        <v>126</v>
       </c>
       <c r="H32" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+      <c r="I32" t="s">
+        <v>322</v>
+      </c>
+      <c r="J32" t="s">
+        <v>1</v>
+      </c>
+      <c r="K32" t="s">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>1</v>
+      </c>
+      <c r="N32" t="s">
+        <v>1</v>
+      </c>
+      <c r="O32" t="s">
+        <v>1</v>
+      </c>
+      <c r="P32" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s">
-        <v>287</v>
+        <v>324</v>
       </c>
       <c r="C33" t="s">
         <v>24</v>
@@ -4118,24 +5066,51 @@
         <v>19</v>
       </c>
       <c r="E33" t="s">
-        <v>288</v>
+        <v>325</v>
       </c>
       <c r="F33" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="G33" t="s">
-        <v>290</v>
+        <v>126</v>
       </c>
       <c r="H33" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+      <c r="I33" t="s">
+        <v>328</v>
+      </c>
+      <c r="J33" t="s">
+        <v>1</v>
+      </c>
+      <c r="K33" t="s">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>1</v>
+      </c>
+      <c r="N33" t="s">
+        <v>1</v>
+      </c>
+      <c r="O33" t="s">
+        <v>1</v>
+      </c>
+      <c r="P33" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="C34" t="s">
         <v>24</v>
@@ -4144,24 +5119,51 @@
         <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="F34" t="s">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="G34" t="s">
-        <v>296</v>
+        <v>126</v>
       </c>
       <c r="H34" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+      <c r="I34" t="s">
+        <v>334</v>
+      </c>
+      <c r="J34" t="s">
+        <v>1</v>
+      </c>
+      <c r="K34" t="s">
+        <v>1</v>
+      </c>
+      <c r="L34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M34" t="s">
+        <v>1</v>
+      </c>
+      <c r="N34" t="s">
+        <v>1</v>
+      </c>
+      <c r="O34" t="s">
+        <v>1</v>
+      </c>
+      <c r="P34" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="B35" t="s">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="C35" t="s">
         <v>24</v>
@@ -4170,24 +5172,51 @@
         <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="F35" t="s">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="G35" t="s">
-        <v>302</v>
+        <v>126</v>
       </c>
       <c r="H35" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="I35" t="s">
+        <v>340</v>
+      </c>
+      <c r="J35" t="s">
+        <v>1</v>
+      </c>
+      <c r="K35" t="s">
+        <v>1</v>
+      </c>
+      <c r="L35" t="s">
+        <v>1</v>
+      </c>
+      <c r="M35" t="s">
+        <v>1</v>
+      </c>
+      <c r="N35" t="s">
+        <v>1</v>
+      </c>
+      <c r="O35" t="s">
+        <v>1</v>
+      </c>
+      <c r="P35" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="C36" t="s">
         <v>24</v>
@@ -4196,24 +5225,51 @@
         <v>19</v>
       </c>
       <c r="E36" t="s">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c r="F36" t="s">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="G36" t="s">
-        <v>308</v>
+        <v>126</v>
       </c>
       <c r="H36" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+      <c r="I36" t="s">
+        <v>346</v>
+      </c>
+      <c r="J36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K36" t="s">
+        <v>1</v>
+      </c>
+      <c r="L36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M36" t="s">
+        <v>1</v>
+      </c>
+      <c r="N36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O36" t="s">
+        <v>1</v>
+      </c>
+      <c r="P36" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="C37" t="s">
         <v>24</v>
@@ -4222,24 +5278,51 @@
         <v>19</v>
       </c>
       <c r="E37" t="s">
-        <v>312</v>
+        <v>349</v>
       </c>
       <c r="F37" t="s">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="G37" t="s">
-        <v>314</v>
+        <v>126</v>
       </c>
       <c r="H37" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+      <c r="I37" t="s">
+        <v>352</v>
+      </c>
+      <c r="J37" t="s">
+        <v>1</v>
+      </c>
+      <c r="K37" t="s">
+        <v>1</v>
+      </c>
+      <c r="L37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M37" t="s">
+        <v>1</v>
+      </c>
+      <c r="N37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O37" t="s">
+        <v>1</v>
+      </c>
+      <c r="P37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="C38" t="s">
         <v>24</v>
@@ -4248,24 +5331,51 @@
         <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>318</v>
+        <v>355</v>
       </c>
       <c r="F38" t="s">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="G38" t="s">
-        <v>320</v>
+        <v>126</v>
       </c>
       <c r="H38" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+      <c r="I38" t="s">
+        <v>358</v>
+      </c>
+      <c r="J38" t="s">
+        <v>1</v>
+      </c>
+      <c r="K38" t="s">
+        <v>1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>1</v>
+      </c>
+      <c r="M38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N38" t="s">
+        <v>1</v>
+      </c>
+      <c r="O38" t="s">
+        <v>1</v>
+      </c>
+      <c r="P38" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>322</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s">
-        <v>323</v>
+        <v>360</v>
       </c>
       <c r="C39" t="s">
         <v>24</v>
@@ -4274,24 +5384,51 @@
         <v>19</v>
       </c>
       <c r="E39" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="F39" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="G39" t="s">
-        <v>326</v>
+        <v>126</v>
       </c>
       <c r="H39" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+      <c r="I39" t="s">
+        <v>364</v>
+      </c>
+      <c r="J39" t="s">
+        <v>1</v>
+      </c>
+      <c r="K39" t="s">
+        <v>1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>1</v>
+      </c>
+      <c r="M39" t="s">
+        <v>1</v>
+      </c>
+      <c r="N39" t="s">
+        <v>1</v>
+      </c>
+      <c r="O39" t="s">
+        <v>1</v>
+      </c>
+      <c r="P39" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="C40" t="s">
         <v>24</v>
@@ -4300,24 +5437,51 @@
         <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="F40" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="G40" t="s">
-        <v>332</v>
+        <v>126</v>
       </c>
       <c r="H40" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="I40" t="s">
+        <v>370</v>
+      </c>
+      <c r="J40" t="s">
+        <v>1</v>
+      </c>
+      <c r="K40" t="s">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>1</v>
+      </c>
+      <c r="M40" t="s">
+        <v>1</v>
+      </c>
+      <c r="N40" t="s">
+        <v>1</v>
+      </c>
+      <c r="O40" t="s">
+        <v>1</v>
+      </c>
+      <c r="P40" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="C41" t="s">
         <v>26</v>
@@ -4326,24 +5490,51 @@
         <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="F41" t="s">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="G41" t="s">
-        <v>338</v>
+        <v>126</v>
       </c>
       <c r="H41" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="I41" t="s">
+        <v>376</v>
+      </c>
+      <c r="J41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K41" t="s">
+        <v>1</v>
+      </c>
+      <c r="L41" t="s">
+        <v>1</v>
+      </c>
+      <c r="M41" t="s">
+        <v>1</v>
+      </c>
+      <c r="N41" t="s">
+        <v>1</v>
+      </c>
+      <c r="O41" t="s">
+        <v>1</v>
+      </c>
+      <c r="P41" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="C42" t="s">
         <v>26</v>
@@ -4352,24 +5543,51 @@
         <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>342</v>
+        <v>379</v>
       </c>
       <c r="F42" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="G42" t="s">
-        <v>344</v>
+        <v>126</v>
       </c>
       <c r="H42" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+      <c r="I42" t="s">
+        <v>382</v>
+      </c>
+      <c r="J42" t="s">
+        <v>1</v>
+      </c>
+      <c r="K42" t="s">
+        <v>1</v>
+      </c>
+      <c r="L42" t="s">
+        <v>1</v>
+      </c>
+      <c r="M42" t="s">
+        <v>1</v>
+      </c>
+      <c r="N42" t="s">
+        <v>1</v>
+      </c>
+      <c r="O42" t="s">
+        <v>1</v>
+      </c>
+      <c r="P42" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="C43" t="s">
         <v>26</v>
@@ -4378,24 +5596,51 @@
         <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>348</v>
+        <v>385</v>
       </c>
       <c r="F43" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="G43" t="s">
-        <v>350</v>
+        <v>126</v>
       </c>
       <c r="H43" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+      <c r="I43" t="s">
+        <v>388</v>
+      </c>
+      <c r="J43" t="s">
+        <v>1</v>
+      </c>
+      <c r="K43" t="s">
+        <v>1</v>
+      </c>
+      <c r="L43" t="s">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>1</v>
+      </c>
+      <c r="N43" t="s">
+        <v>1</v>
+      </c>
+      <c r="O43" t="s">
+        <v>1</v>
+      </c>
+      <c r="P43" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="B44" t="s">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="C44" t="s">
         <v>26</v>
@@ -4404,24 +5649,51 @@
         <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="F44" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="G44" t="s">
-        <v>356</v>
+        <v>126</v>
       </c>
       <c r="H44" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="I44" t="s">
+        <v>394</v>
+      </c>
+      <c r="J44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K44" t="s">
+        <v>1</v>
+      </c>
+      <c r="L44" t="s">
+        <v>1</v>
+      </c>
+      <c r="M44" t="s">
+        <v>1</v>
+      </c>
+      <c r="N44" t="s">
+        <v>1</v>
+      </c>
+      <c r="O44" t="s">
+        <v>1</v>
+      </c>
+      <c r="P44" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="C45" t="s">
         <v>26</v>
@@ -4430,24 +5702,51 @@
         <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="F45" t="s">
-        <v>361</v>
+        <v>398</v>
       </c>
       <c r="G45" t="s">
-        <v>362</v>
+        <v>126</v>
       </c>
       <c r="H45" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+      <c r="I45" t="s">
+        <v>400</v>
+      </c>
+      <c r="J45" t="s">
+        <v>1</v>
+      </c>
+      <c r="K45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L45" t="s">
+        <v>1</v>
+      </c>
+      <c r="M45" t="s">
+        <v>1</v>
+      </c>
+      <c r="N45" t="s">
+        <v>1</v>
+      </c>
+      <c r="O45" t="s">
+        <v>1</v>
+      </c>
+      <c r="P45" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>364</v>
+        <v>401</v>
       </c>
       <c r="B46" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="C46" t="s">
         <v>26</v>
@@ -4456,24 +5755,51 @@
         <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="F46" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="G46" t="s">
-        <v>368</v>
+        <v>126</v>
       </c>
       <c r="H46" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+      <c r="I46" t="s">
+        <v>406</v>
+      </c>
+      <c r="J46" t="s">
+        <v>1</v>
+      </c>
+      <c r="K46" t="s">
+        <v>1</v>
+      </c>
+      <c r="L46" t="s">
+        <v>1</v>
+      </c>
+      <c r="M46" t="s">
+        <v>1</v>
+      </c>
+      <c r="N46" t="s">
+        <v>1</v>
+      </c>
+      <c r="O46" t="s">
+        <v>1</v>
+      </c>
+      <c r="P46" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="C47" t="s">
         <v>26</v>
@@ -4482,24 +5808,51 @@
         <v>19</v>
       </c>
       <c r="E47" t="s">
-        <v>372</v>
+        <v>409</v>
       </c>
       <c r="F47" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="G47" t="s">
-        <v>374</v>
+        <v>126</v>
       </c>
       <c r="H47" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+      <c r="I47" t="s">
+        <v>412</v>
+      </c>
+      <c r="J47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K47" t="s">
+        <v>1</v>
+      </c>
+      <c r="L47" t="s">
+        <v>1</v>
+      </c>
+      <c r="M47" t="s">
+        <v>1</v>
+      </c>
+      <c r="N47" t="s">
+        <v>1</v>
+      </c>
+      <c r="O47" t="s">
+        <v>1</v>
+      </c>
+      <c r="P47" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="C48" t="s">
         <v>26</v>
@@ -4508,24 +5861,51 @@
         <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="F48" t="s">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="G48" t="s">
-        <v>380</v>
+        <v>126</v>
       </c>
       <c r="H48" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+      <c r="I48" t="s">
+        <v>418</v>
+      </c>
+      <c r="J48" t="s">
+        <v>1</v>
+      </c>
+      <c r="K48" t="s">
+        <v>1</v>
+      </c>
+      <c r="L48" t="s">
+        <v>1</v>
+      </c>
+      <c r="M48" t="s">
+        <v>1</v>
+      </c>
+      <c r="N48" t="s">
+        <v>1</v>
+      </c>
+      <c r="O48" t="s">
+        <v>1</v>
+      </c>
+      <c r="P48" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s">
-        <v>383</v>
+        <v>420</v>
       </c>
       <c r="C49" t="s">
         <v>26</v>
@@ -4534,24 +5914,51 @@
         <v>19</v>
       </c>
       <c r="E49" t="s">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="F49" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="G49" t="s">
-        <v>386</v>
+        <v>126</v>
       </c>
       <c r="H49" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>423</v>
+      </c>
+      <c r="I49" t="s">
+        <v>424</v>
+      </c>
+      <c r="J49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L49" t="s">
+        <v>1</v>
+      </c>
+      <c r="M49" t="s">
+        <v>1</v>
+      </c>
+      <c r="N49" t="s">
+        <v>1</v>
+      </c>
+      <c r="O49" t="s">
+        <v>1</v>
+      </c>
+      <c r="P49" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>388</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="C50" t="s">
         <v>26</v>
@@ -4560,24 +5967,51 @@
         <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="F50" t="s">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="G50" t="s">
-        <v>392</v>
+        <v>126</v>
       </c>
       <c r="H50" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+      <c r="I50" t="s">
+        <v>430</v>
+      </c>
+      <c r="J50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N50" t="s">
+        <v>1</v>
+      </c>
+      <c r="O50" t="s">
+        <v>1</v>
+      </c>
+      <c r="P50" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="B51" t="s">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="C51" t="s">
         <v>26</v>
@@ -4586,24 +6020,51 @@
         <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="F51" t="s">
-        <v>397</v>
+        <v>434</v>
       </c>
       <c r="G51" t="s">
-        <v>398</v>
+        <v>126</v>
       </c>
       <c r="H51" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+      <c r="I51" t="s">
+        <v>436</v>
+      </c>
+      <c r="J51" t="s">
+        <v>1</v>
+      </c>
+      <c r="K51" t="s">
+        <v>1</v>
+      </c>
+      <c r="L51" t="s">
+        <v>1</v>
+      </c>
+      <c r="M51" t="s">
+        <v>1</v>
+      </c>
+      <c r="N51" t="s">
+        <v>1</v>
+      </c>
+      <c r="O51" t="s">
+        <v>1</v>
+      </c>
+      <c r="P51" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="B52" t="s">
-        <v>401</v>
+        <v>438</v>
       </c>
       <c r="C52" t="s">
         <v>26</v>
@@ -4612,24 +6073,51 @@
         <v>19</v>
       </c>
       <c r="E52" t="s">
-        <v>402</v>
+        <v>439</v>
       </c>
       <c r="F52" t="s">
-        <v>403</v>
+        <v>440</v>
       </c>
       <c r="G52" t="s">
-        <v>404</v>
+        <v>126</v>
       </c>
       <c r="H52" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+      <c r="I52" t="s">
+        <v>442</v>
+      </c>
+      <c r="J52" t="s">
+        <v>1</v>
+      </c>
+      <c r="K52" t="s">
+        <v>1</v>
+      </c>
+      <c r="L52" t="s">
+        <v>1</v>
+      </c>
+      <c r="M52" t="s">
+        <v>1</v>
+      </c>
+      <c r="N52" t="s">
+        <v>1</v>
+      </c>
+      <c r="O52" t="s">
+        <v>1</v>
+      </c>
+      <c r="P52" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="B53" t="s">
-        <v>407</v>
+        <v>444</v>
       </c>
       <c r="C53" t="s">
         <v>26</v>
@@ -4638,24 +6126,51 @@
         <v>19</v>
       </c>
       <c r="E53" t="s">
-        <v>408</v>
+        <v>445</v>
       </c>
       <c r="F53" t="s">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="G53" t="s">
-        <v>410</v>
+        <v>126</v>
       </c>
       <c r="H53" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+      <c r="I53" t="s">
+        <v>448</v>
+      </c>
+      <c r="J53" t="s">
+        <v>1</v>
+      </c>
+      <c r="K53" t="s">
+        <v>1</v>
+      </c>
+      <c r="L53" t="s">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>1</v>
+      </c>
+      <c r="N53" t="s">
+        <v>1</v>
+      </c>
+      <c r="O53" t="s">
+        <v>1</v>
+      </c>
+      <c r="P53" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>412</v>
+        <v>449</v>
       </c>
       <c r="B54" t="s">
-        <v>413</v>
+        <v>450</v>
       </c>
       <c r="C54" t="s">
         <v>28</v>
@@ -4664,24 +6179,51 @@
         <v>19</v>
       </c>
       <c r="E54" t="s">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="F54" t="s">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="G54" t="s">
-        <v>416</v>
+        <v>126</v>
       </c>
       <c r="H54" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+      <c r="I54" t="s">
+        <v>454</v>
+      </c>
+      <c r="J54" t="s">
+        <v>1</v>
+      </c>
+      <c r="K54" t="s">
+        <v>1</v>
+      </c>
+      <c r="L54" t="s">
+        <v>1</v>
+      </c>
+      <c r="M54" t="s">
+        <v>1</v>
+      </c>
+      <c r="N54" t="s">
+        <v>1</v>
+      </c>
+      <c r="O54" t="s">
+        <v>1</v>
+      </c>
+      <c r="P54" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="C55" t="s">
         <v>28</v>
@@ -4690,24 +6232,51 @@
         <v>19</v>
       </c>
       <c r="E55" t="s">
-        <v>420</v>
+        <v>457</v>
       </c>
       <c r="F55" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="G55" t="s">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="H55" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+      <c r="I55" t="s">
+        <v>460</v>
+      </c>
+      <c r="J55" t="s">
+        <v>1</v>
+      </c>
+      <c r="K55" t="s">
+        <v>1</v>
+      </c>
+      <c r="L55" t="s">
+        <v>1</v>
+      </c>
+      <c r="M55" t="s">
+        <v>1</v>
+      </c>
+      <c r="N55" t="s">
+        <v>1</v>
+      </c>
+      <c r="O55" t="s">
+        <v>1</v>
+      </c>
+      <c r="P55" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="B56" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="C56" t="s">
         <v>28</v>
@@ -4716,24 +6285,51 @@
         <v>19</v>
       </c>
       <c r="E56" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="F56" t="s">
-        <v>427</v>
+        <v>464</v>
       </c>
       <c r="G56" t="s">
-        <v>428</v>
+        <v>126</v>
       </c>
       <c r="H56" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+        <v>465</v>
+      </c>
+      <c r="I56" t="s">
+        <v>466</v>
+      </c>
+      <c r="J56" t="s">
+        <v>1</v>
+      </c>
+      <c r="K56" t="s">
+        <v>1</v>
+      </c>
+      <c r="L56" t="s">
+        <v>1</v>
+      </c>
+      <c r="M56" t="s">
+        <v>1</v>
+      </c>
+      <c r="N56" t="s">
+        <v>1</v>
+      </c>
+      <c r="O56" t="s">
+        <v>1</v>
+      </c>
+      <c r="P56" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>430</v>
+        <v>467</v>
       </c>
       <c r="B57" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="C57" t="s">
         <v>28</v>
@@ -4742,24 +6338,51 @@
         <v>19</v>
       </c>
       <c r="E57" t="s">
-        <v>432</v>
+        <v>469</v>
       </c>
       <c r="F57" t="s">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="G57" t="s">
-        <v>434</v>
+        <v>126</v>
       </c>
       <c r="H57" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+      <c r="I57" t="s">
+        <v>472</v>
+      </c>
+      <c r="J57" t="s">
+        <v>1</v>
+      </c>
+      <c r="K57" t="s">
+        <v>1</v>
+      </c>
+      <c r="L57" t="s">
+        <v>1</v>
+      </c>
+      <c r="M57" t="s">
+        <v>1</v>
+      </c>
+      <c r="N57" t="s">
+        <v>1</v>
+      </c>
+      <c r="O57" t="s">
+        <v>1</v>
+      </c>
+      <c r="P57" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="B58" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="C58" t="s">
         <v>28</v>
@@ -4768,24 +6391,51 @@
         <v>19</v>
       </c>
       <c r="E58" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="F58" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="G58" t="s">
-        <v>440</v>
+        <v>126</v>
       </c>
       <c r="H58" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+        <v>477</v>
+      </c>
+      <c r="I58" t="s">
+        <v>478</v>
+      </c>
+      <c r="J58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L58" t="s">
+        <v>1</v>
+      </c>
+      <c r="M58" t="s">
+        <v>1</v>
+      </c>
+      <c r="N58" t="s">
+        <v>1</v>
+      </c>
+      <c r="O58" t="s">
+        <v>1</v>
+      </c>
+      <c r="P58" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="B59" t="s">
-        <v>443</v>
+        <v>480</v>
       </c>
       <c r="C59" t="s">
         <v>28</v>
@@ -4794,24 +6444,51 @@
         <v>19</v>
       </c>
       <c r="E59" t="s">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="F59" t="s">
-        <v>445</v>
+        <v>482</v>
       </c>
       <c r="G59" t="s">
-        <v>446</v>
+        <v>126</v>
       </c>
       <c r="H59" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+        <v>483</v>
+      </c>
+      <c r="I59" t="s">
+        <v>484</v>
+      </c>
+      <c r="J59" t="s">
+        <v>1</v>
+      </c>
+      <c r="K59" t="s">
+        <v>1</v>
+      </c>
+      <c r="L59" t="s">
+        <v>1</v>
+      </c>
+      <c r="M59" t="s">
+        <v>1</v>
+      </c>
+      <c r="N59" t="s">
+        <v>1</v>
+      </c>
+      <c r="O59" t="s">
+        <v>1</v>
+      </c>
+      <c r="P59" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="B60" t="s">
-        <v>449</v>
+        <v>486</v>
       </c>
       <c r="C60" t="s">
         <v>28</v>
@@ -4820,24 +6497,51 @@
         <v>19</v>
       </c>
       <c r="E60" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="F60" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="G60" t="s">
-        <v>452</v>
+        <v>126</v>
       </c>
       <c r="H60" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+      <c r="I60" t="s">
+        <v>490</v>
+      </c>
+      <c r="J60" t="s">
+        <v>1</v>
+      </c>
+      <c r="K60" t="s">
+        <v>1</v>
+      </c>
+      <c r="L60" t="s">
+        <v>1</v>
+      </c>
+      <c r="M60" t="s">
+        <v>1</v>
+      </c>
+      <c r="N60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O60" t="s">
+        <v>1</v>
+      </c>
+      <c r="P60" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>454</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="C61" t="s">
         <v>28</v>
@@ -4846,24 +6550,51 @@
         <v>19</v>
       </c>
       <c r="E61" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="F61" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
       <c r="G61" t="s">
-        <v>458</v>
+        <v>126</v>
       </c>
       <c r="H61" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+        <v>495</v>
+      </c>
+      <c r="I61" t="s">
+        <v>496</v>
+      </c>
+      <c r="J61" t="s">
+        <v>1</v>
+      </c>
+      <c r="K61" t="s">
+        <v>1</v>
+      </c>
+      <c r="L61" t="s">
+        <v>1</v>
+      </c>
+      <c r="M61" t="s">
+        <v>1</v>
+      </c>
+      <c r="N61" t="s">
+        <v>1</v>
+      </c>
+      <c r="O61" t="s">
+        <v>1</v>
+      </c>
+      <c r="P61" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
       <c r="B62" t="s">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="C62" t="s">
         <v>28</v>
@@ -4872,24 +6603,51 @@
         <v>19</v>
       </c>
       <c r="E62" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="F62" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="G62" t="s">
-        <v>464</v>
+        <v>126</v>
       </c>
       <c r="H62" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+      <c r="I62" t="s">
+        <v>502</v>
+      </c>
+      <c r="J62" t="s">
+        <v>1</v>
+      </c>
+      <c r="K62" t="s">
+        <v>1</v>
+      </c>
+      <c r="L62" t="s">
+        <v>1</v>
+      </c>
+      <c r="M62" t="s">
+        <v>1</v>
+      </c>
+      <c r="N62" t="s">
+        <v>1</v>
+      </c>
+      <c r="O62" t="s">
+        <v>1</v>
+      </c>
+      <c r="P62" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="B63" t="s">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="C63" t="s">
         <v>28</v>
@@ -4898,24 +6656,51 @@
         <v>19</v>
       </c>
       <c r="E63" t="s">
-        <v>468</v>
+        <v>505</v>
       </c>
       <c r="F63" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
       <c r="G63" t="s">
-        <v>470</v>
+        <v>126</v>
       </c>
       <c r="H63" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+      <c r="I63" t="s">
+        <v>508</v>
+      </c>
+      <c r="J63" t="s">
+        <v>1</v>
+      </c>
+      <c r="K63" t="s">
+        <v>1</v>
+      </c>
+      <c r="L63" t="s">
+        <v>1</v>
+      </c>
+      <c r="M63" t="s">
+        <v>1</v>
+      </c>
+      <c r="N63" t="s">
+        <v>1</v>
+      </c>
+      <c r="O63" t="s">
+        <v>1</v>
+      </c>
+      <c r="P63" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>472</v>
+        <v>509</v>
       </c>
       <c r="B64" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="C64" t="s">
         <v>28</v>
@@ -4924,24 +6709,51 @@
         <v>19</v>
       </c>
       <c r="E64" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="F64" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="G64" t="s">
-        <v>476</v>
+        <v>126</v>
       </c>
       <c r="H64" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+      <c r="I64" t="s">
+        <v>514</v>
+      </c>
+      <c r="J64" t="s">
+        <v>1</v>
+      </c>
+      <c r="K64" t="s">
+        <v>1</v>
+      </c>
+      <c r="L64" t="s">
+        <v>1</v>
+      </c>
+      <c r="M64" t="s">
+        <v>1</v>
+      </c>
+      <c r="N64" t="s">
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
+        <v>1</v>
+      </c>
+      <c r="P64" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="B65" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="C65" t="s">
         <v>28</v>
@@ -4950,24 +6762,51 @@
         <v>19</v>
       </c>
       <c r="E65" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="F65" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="G65" t="s">
-        <v>482</v>
+        <v>126</v>
       </c>
       <c r="H65" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+      <c r="I65" t="s">
+        <v>520</v>
+      </c>
+      <c r="J65" t="s">
+        <v>1</v>
+      </c>
+      <c r="K65" t="s">
+        <v>1</v>
+      </c>
+      <c r="L65" t="s">
+        <v>1</v>
+      </c>
+      <c r="M65" t="s">
+        <v>1</v>
+      </c>
+      <c r="N65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O65" t="s">
+        <v>1</v>
+      </c>
+      <c r="P65" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="B66" t="s">
-        <v>485</v>
+        <v>522</v>
       </c>
       <c r="C66" t="s">
         <v>28</v>
@@ -4976,24 +6815,51 @@
         <v>19</v>
       </c>
       <c r="E66" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
       <c r="F66" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="G66" t="s">
-        <v>488</v>
+        <v>126</v>
       </c>
       <c r="H66" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+      <c r="I66" t="s">
+        <v>526</v>
+      </c>
+      <c r="J66" t="s">
+        <v>1</v>
+      </c>
+      <c r="K66" t="s">
+        <v>1</v>
+      </c>
+      <c r="L66" t="s">
+        <v>1</v>
+      </c>
+      <c r="M66" t="s">
+        <v>1</v>
+      </c>
+      <c r="N66" t="s">
+        <v>1</v>
+      </c>
+      <c r="O66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P66" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>490</v>
+        <v>527</v>
       </c>
       <c r="B67" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="C67" t="s">
         <v>30</v>
@@ -5002,24 +6868,51 @@
         <v>19</v>
       </c>
       <c r="E67" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="F67" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="G67" t="s">
-        <v>494</v>
+        <v>126</v>
       </c>
       <c r="H67" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+      <c r="I67" t="s">
+        <v>532</v>
+      </c>
+      <c r="J67" t="s">
+        <v>1</v>
+      </c>
+      <c r="K67" t="s">
+        <v>1</v>
+      </c>
+      <c r="L67" t="s">
+        <v>1</v>
+      </c>
+      <c r="M67" t="s">
+        <v>1</v>
+      </c>
+      <c r="N67" t="s">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>1</v>
+      </c>
+      <c r="P67" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>496</v>
+        <v>533</v>
       </c>
       <c r="B68" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="C68" t="s">
         <v>30</v>
@@ -5028,24 +6921,51 @@
         <v>19</v>
       </c>
       <c r="E68" t="s">
-        <v>498</v>
+        <v>535</v>
       </c>
       <c r="F68" t="s">
-        <v>499</v>
+        <v>536</v>
       </c>
       <c r="G68" t="s">
-        <v>500</v>
+        <v>126</v>
       </c>
       <c r="H68" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+        <v>537</v>
+      </c>
+      <c r="I68" t="s">
+        <v>538</v>
+      </c>
+      <c r="J68" t="s">
+        <v>1</v>
+      </c>
+      <c r="K68" t="s">
+        <v>1</v>
+      </c>
+      <c r="L68" t="s">
+        <v>1</v>
+      </c>
+      <c r="M68" t="s">
+        <v>1</v>
+      </c>
+      <c r="N68" t="s">
+        <v>1</v>
+      </c>
+      <c r="O68" t="s">
+        <v>1</v>
+      </c>
+      <c r="P68" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="B69" t="s">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="C69" t="s">
         <v>30</v>
@@ -5054,24 +6974,51 @@
         <v>19</v>
       </c>
       <c r="E69" t="s">
-        <v>504</v>
+        <v>541</v>
       </c>
       <c r="F69" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="G69" t="s">
-        <v>506</v>
+        <v>126</v>
       </c>
       <c r="H69" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+      <c r="I69" t="s">
+        <v>544</v>
+      </c>
+      <c r="J69" t="s">
+        <v>1</v>
+      </c>
+      <c r="K69" t="s">
+        <v>1</v>
+      </c>
+      <c r="L69" t="s">
+        <v>1</v>
+      </c>
+      <c r="M69" t="s">
+        <v>1</v>
+      </c>
+      <c r="N69" t="s">
+        <v>1</v>
+      </c>
+      <c r="O69" t="s">
+        <v>1</v>
+      </c>
+      <c r="P69" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>508</v>
+        <v>545</v>
       </c>
       <c r="B70" t="s">
-        <v>509</v>
+        <v>546</v>
       </c>
       <c r="C70" t="s">
         <v>30</v>
@@ -5080,24 +7027,51 @@
         <v>19</v>
       </c>
       <c r="E70" t="s">
-        <v>510</v>
+        <v>547</v>
       </c>
       <c r="F70" t="s">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="G70" t="s">
-        <v>512</v>
+        <v>126</v>
       </c>
       <c r="H70" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+        <v>549</v>
+      </c>
+      <c r="I70" t="s">
+        <v>550</v>
+      </c>
+      <c r="J70" t="s">
+        <v>1</v>
+      </c>
+      <c r="K70" t="s">
+        <v>1</v>
+      </c>
+      <c r="L70" t="s">
+        <v>1</v>
+      </c>
+      <c r="M70" t="s">
+        <v>1</v>
+      </c>
+      <c r="N70" t="s">
+        <v>1</v>
+      </c>
+      <c r="O70" t="s">
+        <v>1</v>
+      </c>
+      <c r="P70" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>514</v>
+        <v>551</v>
       </c>
       <c r="B71" t="s">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="C71" t="s">
         <v>30</v>
@@ -5106,24 +7080,51 @@
         <v>19</v>
       </c>
       <c r="E71" t="s">
-        <v>516</v>
+        <v>553</v>
       </c>
       <c r="F71" t="s">
-        <v>517</v>
+        <v>554</v>
       </c>
       <c r="G71" t="s">
-        <v>518</v>
+        <v>126</v>
       </c>
       <c r="H71" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+      <c r="I71" t="s">
+        <v>556</v>
+      </c>
+      <c r="J71" t="s">
+        <v>1</v>
+      </c>
+      <c r="K71" t="s">
+        <v>1</v>
+      </c>
+      <c r="L71" t="s">
+        <v>1</v>
+      </c>
+      <c r="M71" t="s">
+        <v>1</v>
+      </c>
+      <c r="N71" t="s">
+        <v>1</v>
+      </c>
+      <c r="O71" t="s">
+        <v>1</v>
+      </c>
+      <c r="P71" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
       <c r="B72" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="C72" t="s">
         <v>30</v>
@@ -5132,24 +7133,51 @@
         <v>19</v>
       </c>
       <c r="E72" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="F72" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
       <c r="G72" t="s">
-        <v>524</v>
+        <v>126</v>
       </c>
       <c r="H72" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+      <c r="I72" t="s">
+        <v>562</v>
+      </c>
+      <c r="J72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K72" t="s">
+        <v>1</v>
+      </c>
+      <c r="L72" t="s">
+        <v>1</v>
+      </c>
+      <c r="M72" t="s">
+        <v>1</v>
+      </c>
+      <c r="N72" t="s">
+        <v>1</v>
+      </c>
+      <c r="O72" t="s">
+        <v>1</v>
+      </c>
+      <c r="P72" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="B73" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="C73" t="s">
         <v>30</v>
@@ -5158,24 +7186,51 @@
         <v>19</v>
       </c>
       <c r="E73" t="s">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="F73" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="G73" t="s">
-        <v>530</v>
+        <v>126</v>
       </c>
       <c r="H73" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+        <v>567</v>
+      </c>
+      <c r="I73" t="s">
+        <v>568</v>
+      </c>
+      <c r="J73" t="s">
+        <v>1</v>
+      </c>
+      <c r="K73" t="s">
+        <v>1</v>
+      </c>
+      <c r="L73" t="s">
+        <v>1</v>
+      </c>
+      <c r="M73" t="s">
+        <v>1</v>
+      </c>
+      <c r="N73" t="s">
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
+        <v>1</v>
+      </c>
+      <c r="P73" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="B74" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="C74" t="s">
         <v>30</v>
@@ -5184,24 +7239,51 @@
         <v>19</v>
       </c>
       <c r="E74" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="F74" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="G74" t="s">
-        <v>536</v>
+        <v>126</v>
       </c>
       <c r="H74" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+      <c r="I74" t="s">
+        <v>574</v>
+      </c>
+      <c r="J74" t="s">
+        <v>1</v>
+      </c>
+      <c r="K74" t="s">
+        <v>1</v>
+      </c>
+      <c r="L74" t="s">
+        <v>1</v>
+      </c>
+      <c r="M74" t="s">
+        <v>1</v>
+      </c>
+      <c r="N74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O74" t="s">
+        <v>1</v>
+      </c>
+      <c r="P74" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="B75" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="C75" t="s">
         <v>30</v>
@@ -5210,24 +7292,51 @@
         <v>19</v>
       </c>
       <c r="E75" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="F75" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="G75" t="s">
-        <v>542</v>
+        <v>126</v>
       </c>
       <c r="H75" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+        <v>579</v>
+      </c>
+      <c r="I75" t="s">
+        <v>580</v>
+      </c>
+      <c r="J75" t="s">
+        <v>1</v>
+      </c>
+      <c r="K75" t="s">
+        <v>1</v>
+      </c>
+      <c r="L75" t="s">
+        <v>1</v>
+      </c>
+      <c r="M75" t="s">
+        <v>1</v>
+      </c>
+      <c r="N75" t="s">
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P75" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="B76" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
       <c r="C76" t="s">
         <v>30</v>
@@ -5236,24 +7345,51 @@
         <v>19</v>
       </c>
       <c r="E76" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
       <c r="F76" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
       <c r="G76" t="s">
-        <v>548</v>
+        <v>126</v>
       </c>
       <c r="H76" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+      <c r="I76" t="s">
+        <v>586</v>
+      </c>
+      <c r="J76" t="s">
+        <v>1</v>
+      </c>
+      <c r="K76" t="s">
+        <v>1</v>
+      </c>
+      <c r="L76" t="s">
+        <v>1</v>
+      </c>
+      <c r="M76" t="s">
+        <v>1</v>
+      </c>
+      <c r="N76" t="s">
+        <v>1</v>
+      </c>
+      <c r="O76" t="s">
+        <v>1</v>
+      </c>
+      <c r="P76" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="B77" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
       <c r="C77" t="s">
         <v>30</v>
@@ -5262,24 +7398,51 @@
         <v>19</v>
       </c>
       <c r="E77" t="s">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="F77" t="s">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="G77" t="s">
-        <v>554</v>
+        <v>126</v>
       </c>
       <c r="H77" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+      <c r="I77" t="s">
+        <v>592</v>
+      </c>
+      <c r="J77" t="s">
+        <v>1</v>
+      </c>
+      <c r="K77" t="s">
+        <v>1</v>
+      </c>
+      <c r="L77" t="s">
+        <v>1</v>
+      </c>
+      <c r="M77" t="s">
+        <v>1</v>
+      </c>
+      <c r="N77" t="s">
+        <v>1</v>
+      </c>
+      <c r="O77" t="s">
+        <v>1</v>
+      </c>
+      <c r="P77" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
       <c r="B78" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
       <c r="C78" t="s">
         <v>30</v>
@@ -5288,24 +7451,51 @@
         <v>19</v>
       </c>
       <c r="E78" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
       <c r="F78" t="s">
-        <v>559</v>
+        <v>596</v>
       </c>
       <c r="G78" t="s">
-        <v>560</v>
+        <v>126</v>
       </c>
       <c r="H78" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+        <v>597</v>
+      </c>
+      <c r="I78" t="s">
+        <v>598</v>
+      </c>
+      <c r="J78" t="s">
+        <v>1</v>
+      </c>
+      <c r="K78" t="s">
+        <v>1</v>
+      </c>
+      <c r="L78" t="s">
+        <v>1</v>
+      </c>
+      <c r="M78" t="s">
+        <v>1</v>
+      </c>
+      <c r="N78" t="s">
+        <v>1</v>
+      </c>
+      <c r="O78" t="s">
+        <v>1</v>
+      </c>
+      <c r="P78" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>562</v>
+        <v>599</v>
       </c>
       <c r="B79" t="s">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="C79" t="s">
         <v>30</v>
@@ -5314,24 +7504,51 @@
         <v>19</v>
       </c>
       <c r="E79" t="s">
-        <v>564</v>
+        <v>601</v>
       </c>
       <c r="F79" t="s">
-        <v>565</v>
+        <v>602</v>
       </c>
       <c r="G79" t="s">
-        <v>566</v>
+        <v>126</v>
       </c>
       <c r="H79" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+        <v>603</v>
+      </c>
+      <c r="I79" t="s">
+        <v>604</v>
+      </c>
+      <c r="J79" t="s">
+        <v>1</v>
+      </c>
+      <c r="K79" t="s">
+        <v>1</v>
+      </c>
+      <c r="L79" t="s">
+        <v>1</v>
+      </c>
+      <c r="M79" t="s">
+        <v>1</v>
+      </c>
+      <c r="N79" t="s">
+        <v>1</v>
+      </c>
+      <c r="O79" t="s">
+        <v>1</v>
+      </c>
+      <c r="P79" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>568</v>
+        <v>605</v>
       </c>
       <c r="B80" t="s">
-        <v>569</v>
+        <v>606</v>
       </c>
       <c r="C80" t="s">
         <v>32</v>
@@ -5340,24 +7557,51 @@
         <v>19</v>
       </c>
       <c r="E80" t="s">
-        <v>570</v>
+        <v>607</v>
       </c>
       <c r="F80" t="s">
-        <v>571</v>
+        <v>608</v>
       </c>
       <c r="G80" t="s">
-        <v>572</v>
+        <v>126</v>
       </c>
       <c r="H80" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+      <c r="I80" t="s">
+        <v>610</v>
+      </c>
+      <c r="J80" t="s">
+        <v>1</v>
+      </c>
+      <c r="K80" t="s">
+        <v>1</v>
+      </c>
+      <c r="L80" t="s">
+        <v>1</v>
+      </c>
+      <c r="M80" t="s">
+        <v>1</v>
+      </c>
+      <c r="N80" t="s">
+        <v>1</v>
+      </c>
+      <c r="O80" t="s">
+        <v>1</v>
+      </c>
+      <c r="P80" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="B81" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="C81" t="s">
         <v>32</v>
@@ -5366,24 +7610,51 @@
         <v>19</v>
       </c>
       <c r="E81" t="s">
-        <v>576</v>
+        <v>613</v>
       </c>
       <c r="F81" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="G81" t="s">
-        <v>578</v>
+        <v>126</v>
       </c>
       <c r="H81" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+        <v>615</v>
+      </c>
+      <c r="I81" t="s">
+        <v>616</v>
+      </c>
+      <c r="J81" t="s">
+        <v>1</v>
+      </c>
+      <c r="K81" t="s">
+        <v>1</v>
+      </c>
+      <c r="L81" t="s">
+        <v>1</v>
+      </c>
+      <c r="M81" t="s">
+        <v>1</v>
+      </c>
+      <c r="N81" t="s">
+        <v>1</v>
+      </c>
+      <c r="O81" t="s">
+        <v>1</v>
+      </c>
+      <c r="P81" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>580</v>
+        <v>617</v>
       </c>
       <c r="B82" t="s">
-        <v>581</v>
+        <v>618</v>
       </c>
       <c r="C82" t="s">
         <v>32</v>
@@ -5392,24 +7663,51 @@
         <v>19</v>
       </c>
       <c r="E82" t="s">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="F82" t="s">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="G82" t="s">
-        <v>584</v>
+        <v>126</v>
       </c>
       <c r="H82" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+      <c r="I82" t="s">
+        <v>622</v>
+      </c>
+      <c r="J82" t="s">
+        <v>1</v>
+      </c>
+      <c r="K82" t="s">
+        <v>1</v>
+      </c>
+      <c r="L82" t="s">
+        <v>1</v>
+      </c>
+      <c r="M82" t="s">
+        <v>1</v>
+      </c>
+      <c r="N82" t="s">
+        <v>1</v>
+      </c>
+      <c r="O82" t="s">
+        <v>1</v>
+      </c>
+      <c r="P82" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>586</v>
+        <v>623</v>
       </c>
       <c r="B83" t="s">
-        <v>587</v>
+        <v>624</v>
       </c>
       <c r="C83" t="s">
         <v>32</v>
@@ -5418,24 +7716,51 @@
         <v>19</v>
       </c>
       <c r="E83" t="s">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="F83" t="s">
-        <v>589</v>
+        <v>626</v>
       </c>
       <c r="G83" t="s">
-        <v>590</v>
+        <v>126</v>
       </c>
       <c r="H83" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+      <c r="I83" t="s">
+        <v>628</v>
+      </c>
+      <c r="J83" t="s">
+        <v>1</v>
+      </c>
+      <c r="K83" t="s">
+        <v>1</v>
+      </c>
+      <c r="L83" t="s">
+        <v>1</v>
+      </c>
+      <c r="M83" t="s">
+        <v>1</v>
+      </c>
+      <c r="N83" t="s">
+        <v>1</v>
+      </c>
+      <c r="O83" t="s">
+        <v>1</v>
+      </c>
+      <c r="P83" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="B84" t="s">
-        <v>593</v>
+        <v>630</v>
       </c>
       <c r="C84" t="s">
         <v>32</v>
@@ -5444,24 +7769,51 @@
         <v>19</v>
       </c>
       <c r="E84" t="s">
-        <v>594</v>
+        <v>631</v>
       </c>
       <c r="F84" t="s">
-        <v>595</v>
+        <v>632</v>
       </c>
       <c r="G84" t="s">
-        <v>596</v>
+        <v>126</v>
       </c>
       <c r="H84" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+        <v>633</v>
+      </c>
+      <c r="I84" t="s">
+        <v>634</v>
+      </c>
+      <c r="J84" t="s">
+        <v>1</v>
+      </c>
+      <c r="K84" t="s">
+        <v>1</v>
+      </c>
+      <c r="L84" t="s">
+        <v>1</v>
+      </c>
+      <c r="M84" t="s">
+        <v>1</v>
+      </c>
+      <c r="N84" t="s">
+        <v>1</v>
+      </c>
+      <c r="O84" t="s">
+        <v>1</v>
+      </c>
+      <c r="P84" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>598</v>
+        <v>635</v>
       </c>
       <c r="B85" t="s">
-        <v>599</v>
+        <v>636</v>
       </c>
       <c r="C85" t="s">
         <v>32</v>
@@ -5470,24 +7822,51 @@
         <v>19</v>
       </c>
       <c r="E85" t="s">
-        <v>600</v>
+        <v>637</v>
       </c>
       <c r="F85" t="s">
-        <v>601</v>
+        <v>638</v>
       </c>
       <c r="G85" t="s">
-        <v>602</v>
+        <v>126</v>
       </c>
       <c r="H85" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+      <c r="I85" t="s">
+        <v>640</v>
+      </c>
+      <c r="J85" t="s">
+        <v>1</v>
+      </c>
+      <c r="K85" t="s">
+        <v>1</v>
+      </c>
+      <c r="L85" t="s">
+        <v>1</v>
+      </c>
+      <c r="M85" t="s">
+        <v>1</v>
+      </c>
+      <c r="N85" t="s">
+        <v>1</v>
+      </c>
+      <c r="O85" t="s">
+        <v>1</v>
+      </c>
+      <c r="P85" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>604</v>
+        <v>641</v>
       </c>
       <c r="B86" t="s">
-        <v>605</v>
+        <v>642</v>
       </c>
       <c r="C86" t="s">
         <v>32</v>
@@ -5496,24 +7875,51 @@
         <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>606</v>
+        <v>643</v>
       </c>
       <c r="F86" t="s">
-        <v>607</v>
+        <v>644</v>
       </c>
       <c r="G86" t="s">
-        <v>608</v>
+        <v>126</v>
       </c>
       <c r="H86" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+        <v>645</v>
+      </c>
+      <c r="I86" t="s">
+        <v>646</v>
+      </c>
+      <c r="J86" t="s">
+        <v>1</v>
+      </c>
+      <c r="K86" t="s">
+        <v>1</v>
+      </c>
+      <c r="L86" t="s">
+        <v>1</v>
+      </c>
+      <c r="M86" t="s">
+        <v>1</v>
+      </c>
+      <c r="N86" t="s">
+        <v>1</v>
+      </c>
+      <c r="O86" t="s">
+        <v>1</v>
+      </c>
+      <c r="P86" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>610</v>
+        <v>647</v>
       </c>
       <c r="B87" t="s">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="C87" t="s">
         <v>32</v>
@@ -5522,24 +7928,51 @@
         <v>19</v>
       </c>
       <c r="E87" t="s">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="F87" t="s">
-        <v>613</v>
+        <v>650</v>
       </c>
       <c r="G87" t="s">
-        <v>614</v>
+        <v>126</v>
       </c>
       <c r="H87" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+      <c r="I87" t="s">
+        <v>652</v>
+      </c>
+      <c r="J87" t="s">
+        <v>1</v>
+      </c>
+      <c r="K87" t="s">
+        <v>1</v>
+      </c>
+      <c r="L87" t="s">
+        <v>1</v>
+      </c>
+      <c r="M87" t="s">
+        <v>1</v>
+      </c>
+      <c r="N87" t="s">
+        <v>1</v>
+      </c>
+      <c r="O87" t="s">
+        <v>1</v>
+      </c>
+      <c r="P87" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>616</v>
+        <v>653</v>
       </c>
       <c r="B88" t="s">
-        <v>617</v>
+        <v>654</v>
       </c>
       <c r="C88" t="s">
         <v>32</v>
@@ -5548,24 +7981,51 @@
         <v>19</v>
       </c>
       <c r="E88" t="s">
-        <v>618</v>
+        <v>655</v>
       </c>
       <c r="F88" t="s">
-        <v>619</v>
+        <v>656</v>
       </c>
       <c r="G88" t="s">
-        <v>620</v>
+        <v>126</v>
       </c>
       <c r="H88" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+        <v>657</v>
+      </c>
+      <c r="I88" t="s">
+        <v>658</v>
+      </c>
+      <c r="J88" t="s">
+        <v>1</v>
+      </c>
+      <c r="K88" t="s">
+        <v>1</v>
+      </c>
+      <c r="L88" t="s">
+        <v>1</v>
+      </c>
+      <c r="M88" t="s">
+        <v>1</v>
+      </c>
+      <c r="N88" t="s">
+        <v>1</v>
+      </c>
+      <c r="O88" t="s">
+        <v>1</v>
+      </c>
+      <c r="P88" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
       <c r="B89" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="C89" t="s">
         <v>32</v>
@@ -5574,24 +8034,51 @@
         <v>19</v>
       </c>
       <c r="E89" t="s">
-        <v>624</v>
+        <v>661</v>
       </c>
       <c r="F89" t="s">
-        <v>625</v>
+        <v>662</v>
       </c>
       <c r="G89" t="s">
-        <v>626</v>
+        <v>126</v>
       </c>
       <c r="H89" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+        <v>663</v>
+      </c>
+      <c r="I89" t="s">
+        <v>664</v>
+      </c>
+      <c r="J89" t="s">
+        <v>1</v>
+      </c>
+      <c r="K89" t="s">
+        <v>1</v>
+      </c>
+      <c r="L89" t="s">
+        <v>1</v>
+      </c>
+      <c r="M89" t="s">
+        <v>1</v>
+      </c>
+      <c r="N89" t="s">
+        <v>1</v>
+      </c>
+      <c r="O89" t="s">
+        <v>1</v>
+      </c>
+      <c r="P89" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>628</v>
+        <v>665</v>
       </c>
       <c r="B90" t="s">
-        <v>629</v>
+        <v>666</v>
       </c>
       <c r="C90" t="s">
         <v>32</v>
@@ -5600,24 +8087,51 @@
         <v>19</v>
       </c>
       <c r="E90" t="s">
-        <v>630</v>
+        <v>667</v>
       </c>
       <c r="F90" t="s">
-        <v>631</v>
+        <v>668</v>
       </c>
       <c r="G90" t="s">
-        <v>632</v>
+        <v>126</v>
       </c>
       <c r="H90" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+        <v>669</v>
+      </c>
+      <c r="I90" t="s">
+        <v>670</v>
+      </c>
+      <c r="J90" t="s">
+        <v>1</v>
+      </c>
+      <c r="K90" t="s">
+        <v>1</v>
+      </c>
+      <c r="L90" t="s">
+        <v>1</v>
+      </c>
+      <c r="M90" t="s">
+        <v>1</v>
+      </c>
+      <c r="N90" t="s">
+        <v>1</v>
+      </c>
+      <c r="O90" t="s">
+        <v>1</v>
+      </c>
+      <c r="P90" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>634</v>
+        <v>671</v>
       </c>
       <c r="B91" t="s">
-        <v>635</v>
+        <v>672</v>
       </c>
       <c r="C91" t="s">
         <v>32</v>
@@ -5626,24 +8140,51 @@
         <v>19</v>
       </c>
       <c r="E91" t="s">
-        <v>636</v>
+        <v>673</v>
       </c>
       <c r="F91" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
       <c r="G91" t="s">
-        <v>638</v>
+        <v>126</v>
       </c>
       <c r="H91" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+        <v>675</v>
+      </c>
+      <c r="I91" t="s">
+        <v>676</v>
+      </c>
+      <c r="J91" t="s">
+        <v>1</v>
+      </c>
+      <c r="K91" t="s">
+        <v>1</v>
+      </c>
+      <c r="L91" t="s">
+        <v>1</v>
+      </c>
+      <c r="M91" t="s">
+        <v>1</v>
+      </c>
+      <c r="N91" t="s">
+        <v>1</v>
+      </c>
+      <c r="O91" t="s">
+        <v>1</v>
+      </c>
+      <c r="P91" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>640</v>
+        <v>677</v>
       </c>
       <c r="B92" t="s">
-        <v>641</v>
+        <v>678</v>
       </c>
       <c r="C92" t="s">
         <v>32</v>
@@ -5652,24 +8193,51 @@
         <v>19</v>
       </c>
       <c r="E92" t="s">
-        <v>642</v>
+        <v>679</v>
       </c>
       <c r="F92" t="s">
-        <v>643</v>
+        <v>680</v>
       </c>
       <c r="G92" t="s">
-        <v>644</v>
+        <v>126</v>
       </c>
       <c r="H92" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+        <v>681</v>
+      </c>
+      <c r="I92" t="s">
+        <v>682</v>
+      </c>
+      <c r="J92" t="s">
+        <v>1</v>
+      </c>
+      <c r="K92" t="s">
+        <v>1</v>
+      </c>
+      <c r="L92" t="s">
+        <v>1</v>
+      </c>
+      <c r="M92" t="s">
+        <v>1</v>
+      </c>
+      <c r="N92" t="s">
+        <v>1</v>
+      </c>
+      <c r="O92" t="s">
+        <v>1</v>
+      </c>
+      <c r="P92" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>646</v>
+        <v>683</v>
       </c>
       <c r="B93" t="s">
-        <v>647</v>
+        <v>684</v>
       </c>
       <c r="C93" t="s">
         <v>34</v>
@@ -5678,24 +8246,51 @@
         <v>19</v>
       </c>
       <c r="E93" t="s">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="F93" t="s">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="G93" t="s">
-        <v>650</v>
+        <v>126</v>
       </c>
       <c r="H93" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+        <v>687</v>
+      </c>
+      <c r="I93" t="s">
+        <v>688</v>
+      </c>
+      <c r="J93" t="s">
+        <v>1</v>
+      </c>
+      <c r="K93" t="s">
+        <v>1</v>
+      </c>
+      <c r="L93" t="s">
+        <v>1</v>
+      </c>
+      <c r="M93" t="s">
+        <v>1</v>
+      </c>
+      <c r="N93" t="s">
+        <v>1</v>
+      </c>
+      <c r="O93" t="s">
+        <v>1</v>
+      </c>
+      <c r="P93" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>652</v>
+        <v>689</v>
       </c>
       <c r="B94" t="s">
-        <v>653</v>
+        <v>690</v>
       </c>
       <c r="C94" t="s">
         <v>34</v>
@@ -5704,24 +8299,51 @@
         <v>19</v>
       </c>
       <c r="E94" t="s">
-        <v>654</v>
+        <v>691</v>
       </c>
       <c r="F94" t="s">
-        <v>655</v>
+        <v>692</v>
       </c>
       <c r="G94" t="s">
-        <v>656</v>
+        <v>126</v>
       </c>
       <c r="H94" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+      <c r="I94" t="s">
+        <v>694</v>
+      </c>
+      <c r="J94" t="s">
+        <v>1</v>
+      </c>
+      <c r="K94" t="s">
+        <v>1</v>
+      </c>
+      <c r="L94" t="s">
+        <v>1</v>
+      </c>
+      <c r="M94" t="s">
+        <v>1</v>
+      </c>
+      <c r="N94" t="s">
+        <v>1</v>
+      </c>
+      <c r="O94" t="s">
+        <v>1</v>
+      </c>
+      <c r="P94" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>658</v>
+        <v>695</v>
       </c>
       <c r="B95" t="s">
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="C95" t="s">
         <v>34</v>
@@ -5730,24 +8352,51 @@
         <v>19</v>
       </c>
       <c r="E95" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="F95" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G95" t="s">
-        <v>662</v>
+        <v>126</v>
       </c>
       <c r="H95" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+      <c r="I95" t="s">
+        <v>700</v>
+      </c>
+      <c r="J95" t="s">
+        <v>1</v>
+      </c>
+      <c r="K95" t="s">
+        <v>1</v>
+      </c>
+      <c r="L95" t="s">
+        <v>1</v>
+      </c>
+      <c r="M95" t="s">
+        <v>1</v>
+      </c>
+      <c r="N95" t="s">
+        <v>1</v>
+      </c>
+      <c r="O95" t="s">
+        <v>1</v>
+      </c>
+      <c r="P95" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>664</v>
+        <v>701</v>
       </c>
       <c r="B96" t="s">
-        <v>665</v>
+        <v>702</v>
       </c>
       <c r="C96" t="s">
         <v>34</v>
@@ -5756,24 +8405,51 @@
         <v>19</v>
       </c>
       <c r="E96" t="s">
-        <v>666</v>
+        <v>703</v>
       </c>
       <c r="F96" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="G96" t="s">
-        <v>668</v>
+        <v>126</v>
       </c>
       <c r="H96" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+      <c r="I96" t="s">
+        <v>706</v>
+      </c>
+      <c r="J96" t="s">
+        <v>1</v>
+      </c>
+      <c r="K96" t="s">
+        <v>1</v>
+      </c>
+      <c r="L96" t="s">
+        <v>1</v>
+      </c>
+      <c r="M96" t="s">
+        <v>1</v>
+      </c>
+      <c r="N96" t="s">
+        <v>1</v>
+      </c>
+      <c r="O96" t="s">
+        <v>1</v>
+      </c>
+      <c r="P96" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="B97" t="s">
-        <v>671</v>
+        <v>708</v>
       </c>
       <c r="C97" t="s">
         <v>34</v>
@@ -5782,24 +8458,51 @@
         <v>19</v>
       </c>
       <c r="E97" t="s">
-        <v>672</v>
+        <v>709</v>
       </c>
       <c r="F97" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G97" t="s">
-        <v>674</v>
+        <v>126</v>
       </c>
       <c r="H97" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+        <v>711</v>
+      </c>
+      <c r="I97" t="s">
+        <v>712</v>
+      </c>
+      <c r="J97" t="s">
+        <v>1</v>
+      </c>
+      <c r="K97" t="s">
+        <v>1</v>
+      </c>
+      <c r="L97" t="s">
+        <v>1</v>
+      </c>
+      <c r="M97" t="s">
+        <v>1</v>
+      </c>
+      <c r="N97" t="s">
+        <v>1</v>
+      </c>
+      <c r="O97" t="s">
+        <v>1</v>
+      </c>
+      <c r="P97" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>676</v>
+        <v>713</v>
       </c>
       <c r="B98" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
       <c r="C98" t="s">
         <v>34</v>
@@ -5808,24 +8511,51 @@
         <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>678</v>
+        <v>715</v>
       </c>
       <c r="F98" t="s">
-        <v>679</v>
+        <v>716</v>
       </c>
       <c r="G98" t="s">
-        <v>680</v>
+        <v>126</v>
       </c>
       <c r="H98" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+        <v>717</v>
+      </c>
+      <c r="I98" t="s">
+        <v>718</v>
+      </c>
+      <c r="J98" t="s">
+        <v>1</v>
+      </c>
+      <c r="K98" t="s">
+        <v>1</v>
+      </c>
+      <c r="L98" t="s">
+        <v>1</v>
+      </c>
+      <c r="M98" t="s">
+        <v>1</v>
+      </c>
+      <c r="N98" t="s">
+        <v>1</v>
+      </c>
+      <c r="O98" t="s">
+        <v>1</v>
+      </c>
+      <c r="P98" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>682</v>
+        <v>719</v>
       </c>
       <c r="B99" t="s">
-        <v>683</v>
+        <v>720</v>
       </c>
       <c r="C99" t="s">
         <v>34</v>
@@ -5834,24 +8564,51 @@
         <v>19</v>
       </c>
       <c r="E99" t="s">
-        <v>684</v>
+        <v>721</v>
       </c>
       <c r="F99" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="G99" t="s">
-        <v>686</v>
+        <v>126</v>
       </c>
       <c r="H99" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+      <c r="I99" t="s">
+        <v>724</v>
+      </c>
+      <c r="J99" t="s">
+        <v>1</v>
+      </c>
+      <c r="K99" t="s">
+        <v>1</v>
+      </c>
+      <c r="L99" t="s">
+        <v>1</v>
+      </c>
+      <c r="M99" t="s">
+        <v>1</v>
+      </c>
+      <c r="N99" t="s">
+        <v>1</v>
+      </c>
+      <c r="O99" t="s">
+        <v>1</v>
+      </c>
+      <c r="P99" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>688</v>
+        <v>725</v>
       </c>
       <c r="B100" t="s">
-        <v>689</v>
+        <v>726</v>
       </c>
       <c r="C100" t="s">
         <v>34</v>
@@ -5860,24 +8617,51 @@
         <v>19</v>
       </c>
       <c r="E100" t="s">
-        <v>690</v>
+        <v>727</v>
       </c>
       <c r="F100" t="s">
-        <v>691</v>
+        <v>728</v>
       </c>
       <c r="G100" t="s">
-        <v>692</v>
+        <v>126</v>
       </c>
       <c r="H100" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+        <v>729</v>
+      </c>
+      <c r="I100" t="s">
+        <v>730</v>
+      </c>
+      <c r="J100" t="s">
+        <v>1</v>
+      </c>
+      <c r="K100" t="s">
+        <v>1</v>
+      </c>
+      <c r="L100" t="s">
+        <v>1</v>
+      </c>
+      <c r="M100" t="s">
+        <v>1</v>
+      </c>
+      <c r="N100" t="s">
+        <v>1</v>
+      </c>
+      <c r="O100" t="s">
+        <v>1</v>
+      </c>
+      <c r="P100" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>694</v>
+        <v>731</v>
       </c>
       <c r="B101" t="s">
-        <v>695</v>
+        <v>732</v>
       </c>
       <c r="C101" t="s">
         <v>34</v>
@@ -5886,24 +8670,51 @@
         <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="F101" t="s">
-        <v>697</v>
+        <v>734</v>
       </c>
       <c r="G101" t="s">
-        <v>698</v>
+        <v>126</v>
       </c>
       <c r="H101" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+        <v>735</v>
+      </c>
+      <c r="I101" t="s">
+        <v>736</v>
+      </c>
+      <c r="J101" t="s">
+        <v>1</v>
+      </c>
+      <c r="K101" t="s">
+        <v>1</v>
+      </c>
+      <c r="L101" t="s">
+        <v>1</v>
+      </c>
+      <c r="M101" t="s">
+        <v>1</v>
+      </c>
+      <c r="N101" t="s">
+        <v>1</v>
+      </c>
+      <c r="O101" t="s">
+        <v>1</v>
+      </c>
+      <c r="P101" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>700</v>
+        <v>737</v>
       </c>
       <c r="B102" t="s">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="C102" t="s">
         <v>34</v>
@@ -5912,24 +8723,51 @@
         <v>19</v>
       </c>
       <c r="E102" t="s">
-        <v>702</v>
+        <v>739</v>
       </c>
       <c r="F102" t="s">
-        <v>703</v>
+        <v>740</v>
       </c>
       <c r="G102" t="s">
-        <v>704</v>
+        <v>126</v>
       </c>
       <c r="H102" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+      <c r="I102" t="s">
+        <v>742</v>
+      </c>
+      <c r="J102" t="s">
+        <v>1</v>
+      </c>
+      <c r="K102" t="s">
+        <v>1</v>
+      </c>
+      <c r="L102" t="s">
+        <v>1</v>
+      </c>
+      <c r="M102" t="s">
+        <v>1</v>
+      </c>
+      <c r="N102" t="s">
+        <v>1</v>
+      </c>
+      <c r="O102" t="s">
+        <v>1</v>
+      </c>
+      <c r="P102" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>706</v>
+        <v>743</v>
       </c>
       <c r="B103" t="s">
-        <v>707</v>
+        <v>744</v>
       </c>
       <c r="C103" t="s">
         <v>34</v>
@@ -5938,24 +8776,51 @@
         <v>19</v>
       </c>
       <c r="E103" t="s">
-        <v>708</v>
+        <v>745</v>
       </c>
       <c r="F103" t="s">
-        <v>709</v>
+        <v>746</v>
       </c>
       <c r="G103" t="s">
-        <v>710</v>
+        <v>126</v>
       </c>
       <c r="H103" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+        <v>747</v>
+      </c>
+      <c r="I103" t="s">
+        <v>748</v>
+      </c>
+      <c r="J103" t="s">
+        <v>1</v>
+      </c>
+      <c r="K103" t="s">
+        <v>1</v>
+      </c>
+      <c r="L103" t="s">
+        <v>1</v>
+      </c>
+      <c r="M103" t="s">
+        <v>1</v>
+      </c>
+      <c r="N103" t="s">
+        <v>1</v>
+      </c>
+      <c r="O103" t="s">
+        <v>1</v>
+      </c>
+      <c r="P103" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>712</v>
+        <v>749</v>
       </c>
       <c r="B104" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
       <c r="C104" t="s">
         <v>34</v>
@@ -5964,24 +8829,51 @@
         <v>19</v>
       </c>
       <c r="E104" t="s">
-        <v>714</v>
+        <v>751</v>
       </c>
       <c r="F104" t="s">
-        <v>715</v>
+        <v>752</v>
       </c>
       <c r="G104" t="s">
-        <v>716</v>
+        <v>126</v>
       </c>
       <c r="H104" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+        <v>753</v>
+      </c>
+      <c r="I104" t="s">
+        <v>754</v>
+      </c>
+      <c r="J104" t="s">
+        <v>1</v>
+      </c>
+      <c r="K104" t="s">
+        <v>1</v>
+      </c>
+      <c r="L104" t="s">
+        <v>1</v>
+      </c>
+      <c r="M104" t="s">
+        <v>1</v>
+      </c>
+      <c r="N104" t="s">
+        <v>1</v>
+      </c>
+      <c r="O104" t="s">
+        <v>1</v>
+      </c>
+      <c r="P104" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>718</v>
+        <v>755</v>
       </c>
       <c r="B105" t="s">
-        <v>719</v>
+        <v>756</v>
       </c>
       <c r="C105" t="s">
         <v>34</v>
@@ -5990,21 +8882,48 @@
         <v>19</v>
       </c>
       <c r="E105" t="s">
-        <v>720</v>
+        <v>757</v>
       </c>
       <c r="F105" t="s">
-        <v>721</v>
+        <v>758</v>
       </c>
       <c r="G105" t="s">
-        <v>722</v>
+        <v>126</v>
       </c>
       <c r="H105" t="s">
-        <v>723</v>
+        <v>759</v>
+      </c>
+      <c r="I105" t="s">
+        <v>760</v>
+      </c>
+      <c r="J105" t="s">
+        <v>1</v>
+      </c>
+      <c r="K105" t="s">
+        <v>1</v>
+      </c>
+      <c r="L105" t="s">
+        <v>1</v>
+      </c>
+      <c r="M105" t="s">
+        <v>1</v>
+      </c>
+      <c r="N105" t="s">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>1</v>
+      </c>
+      <c r="P105" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -6021,22 +8940,22 @@
         <v>14</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>724</v>
+        <v>94</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>725</v>
+        <v>95</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>726</v>
+        <v>96</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>727</v>
+        <v>97</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>728</v>
+        <v>98</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>729</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6047,16 +8966,16 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E2">
         <v>12000</v>
       </c>
       <c r="F2" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -6070,16 +8989,16 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E3">
         <v>3000</v>
       </c>
       <c r="F3" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G3">
         <v>50</v>
@@ -6093,16 +9012,16 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E4">
         <v>1000</v>
       </c>
       <c r="F4" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -6116,16 +9035,16 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E5">
         <v>12000</v>
       </c>
       <c r="F5" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G5">
         <v>50</v>
@@ -6139,16 +9058,16 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E6">
         <v>3000</v>
       </c>
       <c r="F6" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G6">
         <v>50</v>
@@ -6162,16 +9081,16 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E7">
         <v>1000</v>
       </c>
       <c r="F7" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G7">
         <v>50</v>
@@ -6185,16 +9104,16 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E8">
         <v>13500</v>
       </c>
       <c r="F8" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G8">
         <v>50</v>
@@ -6208,16 +9127,16 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E9">
         <v>3200</v>
       </c>
       <c r="F9" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G9">
         <v>50</v>
@@ -6231,16 +9150,16 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E10">
         <v>1100</v>
       </c>
       <c r="F10" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G10">
         <v>50</v>
@@ -6254,16 +9173,16 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E11">
         <v>13500</v>
       </c>
       <c r="F11" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G11">
         <v>50</v>
@@ -6277,16 +9196,16 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E12">
         <v>3200</v>
       </c>
       <c r="F12" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G12">
         <v>50</v>
@@ -6300,16 +9219,16 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E13">
         <v>1100</v>
       </c>
       <c r="F13" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G13">
         <v>50</v>
@@ -6323,16 +9242,16 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E14">
         <v>15000</v>
       </c>
       <c r="F14" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G14">
         <v>50</v>
@@ -6346,16 +9265,16 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E15">
         <v>3400</v>
       </c>
       <c r="F15" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G15">
         <v>50</v>
@@ -6369,16 +9288,16 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E16">
         <v>1200</v>
       </c>
       <c r="F16" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G16">
         <v>50</v>
@@ -6392,16 +9311,16 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E17">
         <v>15000</v>
       </c>
       <c r="F17" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G17">
         <v>50</v>
@@ -6415,16 +9334,16 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E18">
         <v>3400</v>
       </c>
       <c r="F18" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G18">
         <v>50</v>
@@ -6438,16 +9357,16 @@
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E19">
         <v>1200</v>
       </c>
       <c r="F19" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G19">
         <v>50</v>
@@ -6461,16 +9380,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E20">
         <v>16500</v>
       </c>
       <c r="F20" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G20">
         <v>50</v>
@@ -6484,16 +9403,16 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E21">
         <v>3600</v>
       </c>
       <c r="F21" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G21">
         <v>50</v>
@@ -6507,16 +9426,16 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E22">
         <v>1300</v>
       </c>
       <c r="F22" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G22">
         <v>50</v>
@@ -6530,16 +9449,16 @@
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E23">
         <v>16500</v>
       </c>
       <c r="F23" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G23">
         <v>50</v>
@@ -6553,16 +9472,16 @@
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E24">
         <v>3600</v>
       </c>
       <c r="F24" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G24">
         <v>50</v>
@@ -6576,16 +9495,16 @@
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E25">
         <v>1300</v>
       </c>
       <c r="F25" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G25">
         <v>50</v>
@@ -6599,16 +9518,16 @@
         <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E26">
         <v>18000</v>
       </c>
       <c r="F26" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G26">
         <v>50</v>
@@ -6622,16 +9541,16 @@
         <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E27">
         <v>3800</v>
       </c>
       <c r="F27" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G27">
         <v>50</v>
@@ -6645,16 +9564,16 @@
         <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E28">
         <v>1400</v>
       </c>
       <c r="F28" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G28">
         <v>50</v>
@@ -6668,16 +9587,16 @@
         <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E29">
         <v>18000</v>
       </c>
       <c r="F29" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G29">
         <v>50</v>
@@ -6691,16 +9610,16 @@
         <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E30">
         <v>3800</v>
       </c>
       <c r="F30" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G30">
         <v>50</v>
@@ -6714,16 +9633,16 @@
         <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E31">
         <v>1400</v>
       </c>
       <c r="F31" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G31">
         <v>50</v>
@@ -6737,16 +9656,16 @@
         <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E32">
         <v>19500</v>
       </c>
       <c r="F32" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G32">
         <v>50</v>
@@ -6760,16 +9679,16 @@
         <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E33">
         <v>4000</v>
       </c>
       <c r="F33" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G33">
         <v>50</v>
@@ -6783,16 +9702,16 @@
         <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D34" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E34">
         <v>1500</v>
       </c>
       <c r="F34" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G34">
         <v>50</v>
@@ -6806,16 +9725,16 @@
         <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E35">
         <v>19500</v>
       </c>
       <c r="F35" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G35">
         <v>50</v>
@@ -6829,16 +9748,16 @@
         <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E36">
         <v>4000</v>
       </c>
       <c r="F36" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G36">
         <v>50</v>
@@ -6852,16 +9771,16 @@
         <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E37">
         <v>1500</v>
       </c>
       <c r="F37" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G37">
         <v>50</v>
@@ -6875,16 +9794,16 @@
         <v>19</v>
       </c>
       <c r="C38" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D38" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E38">
         <v>21000</v>
       </c>
       <c r="F38" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G38">
         <v>50</v>
@@ -6898,16 +9817,16 @@
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E39">
         <v>4200</v>
       </c>
       <c r="F39" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G39">
         <v>50</v>
@@ -6921,16 +9840,16 @@
         <v>19</v>
       </c>
       <c r="C40" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E40">
         <v>1600</v>
       </c>
       <c r="F40" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G40">
         <v>50</v>
@@ -6944,16 +9863,16 @@
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E41">
         <v>21000</v>
       </c>
       <c r="F41" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G41">
         <v>50</v>
@@ -6967,16 +9886,16 @@
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E42">
         <v>4200</v>
       </c>
       <c r="F42" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G42">
         <v>50</v>
@@ -6990,16 +9909,16 @@
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D43" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E43">
         <v>1600</v>
       </c>
       <c r="F43" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G43">
         <v>50</v>
@@ -7013,16 +9932,16 @@
         <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E44">
         <v>22500</v>
       </c>
       <c r="F44" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G44">
         <v>50</v>
@@ -7036,16 +9955,16 @@
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E45">
         <v>4400</v>
       </c>
       <c r="F45" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G45">
         <v>50</v>
@@ -7059,16 +9978,16 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>730</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E46">
         <v>1700</v>
       </c>
       <c r="F46" t="s">
-        <v>732</v>
+        <v>102</v>
       </c>
       <c r="G46">
         <v>50</v>
@@ -7082,16 +10001,16 @@
         <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D47" t="s">
-        <v>731</v>
+        <v>101</v>
       </c>
       <c r="E47">
         <v>22500</v>
       </c>
       <c r="F47" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G47">
         <v>50</v>
@@ -7105,16 +10024,16 @@
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>733</v>
+        <v>103</v>
       </c>
       <c r="E48">
         <v>4400</v>
       </c>
       <c r="F48" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G48">
         <v>50</v>
@@ -7128,16 +10047,16 @@
         <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>735</v>
+        <v>105</v>
       </c>
       <c r="D49" t="s">
-        <v>734</v>
+        <v>104</v>
       </c>
       <c r="E49">
         <v>1700</v>
       </c>
       <c r="F49" t="s">
-        <v>736</v>
+        <v>106</v>
       </c>
       <c r="G49">
         <v>50</v>
@@ -7172,25 +10091,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>737</v>
+        <v>761</v>
       </c>
       <c r="B1" t="s">
-        <v>738</v>
+        <v>762</v>
       </c>
       <c r="C1" t="s">
-        <v>739</v>
+        <v>763</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>724</v>
+        <v>94</v>
       </c>
       <c r="F1" t="s">
-        <v>740</v>
+        <v>764</v>
       </c>
       <c r="G1" t="s">
-        <v>741</v>
+        <v>765</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -7210,10 +10129,10 @@
         <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>742</v>
+        <v>766</v>
       </c>
       <c r="G2" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7233,10 +10152,10 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>744</v>
+        <v>768</v>
       </c>
       <c r="G3" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7256,10 +10175,10 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>745</v>
+        <v>769</v>
       </c>
       <c r="G4" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7279,10 +10198,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>746</v>
+        <v>770</v>
       </c>
       <c r="G5" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7302,10 +10221,10 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>742</v>
+        <v>766</v>
       </c>
       <c r="G6" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7325,10 +10244,10 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>744</v>
+        <v>768</v>
       </c>
       <c r="G7" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7348,10 +10267,10 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>745</v>
+        <v>769</v>
       </c>
       <c r="G8" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7371,10 +10290,10 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>746</v>
+        <v>770</v>
       </c>
       <c r="G9" t="s">
-        <v>743</v>
+        <v>767</v>
       </c>
     </row>
   </sheetData>
